--- a/database/VAM_connections_data.xlsx
+++ b/database/VAM_connections_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pucriobr-my.sharepoint.com/personal/danielduquemelo_puc-rio_br/Documents/DOUTORADO/TESE/pipe_options/octg_tubulars/VAM/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CODE_REPOSITORIES\pyWellIntegrityToolkit\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{E55A592E-60FC-4AEB-9D44-61A71F1B4108}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6BC53A8-5D13-4FF5-8E75-590518AD5EC6}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35C4C579-8E97-4D18-9714-DA66FD3ED698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5420" yWindow="1370" windowWidth="28800" windowHeight="17750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -43,9 +43,6 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="44">
   <si>
     <t>Connection Type</t>
-  </si>
-  <si>
-    <t>Size (OD)</t>
   </si>
   <si>
     <t>Nominal Weight (lb/ft)</t>
@@ -172,6 +169,9 @@
   </si>
   <si>
     <t xml:space="preserve"> S</t>
+  </si>
+  <si>
+    <t>Size OD (in)</t>
   </si>
 </sst>
 </file>
@@ -628,69 +628,69 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="G1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="P1" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="T1" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="U1" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B2" s="8">
         <v>3.5</v>
@@ -708,10 +708,10 @@
         <v>2.9</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I2" s="10">
         <v>2.9609999999999999</v>
@@ -748,7 +748,7 @@
     </row>
     <row r="3" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" s="8">
         <v>3.6</v>
@@ -767,7 +767,7 @@
       </c>
       <c r="G3" s="9"/>
       <c r="H3" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I3" s="10">
         <v>2.87</v>
@@ -804,7 +804,7 @@
     </row>
     <row r="4" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4" s="8">
         <v>3.7</v>
@@ -823,7 +823,7 @@
       </c>
       <c r="G4" s="9"/>
       <c r="H4" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I4" s="10">
         <v>2.706</v>
@@ -860,7 +860,7 @@
     </row>
     <row r="5" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B5" s="8">
         <v>4.5</v>
@@ -878,10 +878,10 @@
         <v>3.88</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I5" s="10">
         <v>3.9420000000000002</v>
@@ -918,7 +918,7 @@
     </row>
     <row r="6" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B6" s="8">
         <v>4.5999999999999996</v>
@@ -936,10 +936,10 @@
         <v>3.88</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I6" s="10">
         <v>3.9420000000000002</v>
@@ -976,7 +976,7 @@
     </row>
     <row r="7" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" s="8">
         <v>4.7</v>
@@ -994,10 +994,10 @@
         <v>3.8450000000000002</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I7" s="10">
         <v>3.907</v>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="8" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" s="8">
         <v>4.8</v>
@@ -1052,10 +1052,10 @@
         <v>3.75</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I8" s="10">
         <v>3.8119999999999998</v>
@@ -1092,7 +1092,7 @@
     </row>
     <row r="9" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" s="8">
         <v>4.9000000000000004</v>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="G9" s="9"/>
       <c r="H9" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I9" s="10">
         <v>3.7440000000000002</v>
@@ -1148,7 +1148,7 @@
     </row>
     <row r="10" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B10" s="8">
         <v>4.0999999999999996</v>
@@ -1166,10 +1166,10 @@
         <v>3.54</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I10" s="10">
         <v>3.7010000000000001</v>
@@ -1206,7 +1206,7 @@
     </row>
     <row r="11" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B11" s="8">
         <v>4.1100000000000003</v>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="G11" s="9"/>
       <c r="H11" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I11" s="10">
         <v>3.5659999999999998</v>
@@ -1262,7 +1262,7 @@
     </row>
     <row r="12" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B12" s="8">
         <v>5</v>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="G12" s="9"/>
       <c r="H12" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I12" s="10">
         <v>4.2939999999999996</v>
@@ -1318,7 +1318,7 @@
     </row>
     <row r="13" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B13" s="8">
         <v>5</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="G13" s="9"/>
       <c r="H13" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I13" s="10">
         <v>4.1260000000000003</v>
@@ -1374,7 +1374,7 @@
     </row>
     <row r="14" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A14" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B14" s="8">
         <v>5</v>
@@ -1393,7 +1393,7 @@
       </c>
       <c r="G14" s="9"/>
       <c r="H14" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I14" s="10">
         <v>4.0890000000000004</v>
@@ -1430,7 +1430,7 @@
     </row>
     <row r="15" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A15" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B15" s="8">
         <v>5</v>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="G15" s="9"/>
       <c r="H15" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I15" s="10">
         <v>4.069</v>
@@ -1486,7 +1486,7 @@
     </row>
     <row r="16" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A16" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B16" s="8">
         <v>5.5</v>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="G16" s="9"/>
       <c r="H16" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I16" s="10">
         <v>4.891</v>
@@ -1542,7 +1542,7 @@
     </row>
     <row r="17" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A17" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" s="8">
         <v>5.6</v>
@@ -1560,10 +1560,10 @@
         <v>4.7</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I17" s="10">
         <v>4.806</v>
@@ -1600,7 +1600,7 @@
     </row>
     <row r="18" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A18" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B18" s="8">
         <v>5.7</v>
@@ -1619,7 +1619,7 @@
       </c>
       <c r="G18" s="9"/>
       <c r="H18" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I18" s="10">
         <v>4.72</v>
@@ -1656,7 +1656,7 @@
     </row>
     <row r="19" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A19" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B19" s="8">
         <v>5.8</v>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="G19" s="9"/>
       <c r="H19" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I19" s="10">
         <v>4.6150000000000002</v>
@@ -1712,7 +1712,7 @@
     </row>
     <row r="20" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A20" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B20" s="8">
         <v>5.9</v>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="G20" s="9"/>
       <c r="H20" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I20" s="10">
         <v>4.593</v>
@@ -1768,7 +1768,7 @@
     </row>
     <row r="21" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A21" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B21" s="8">
         <v>5.0999999999999996</v>
@@ -1787,7 +1787,7 @@
       </c>
       <c r="G21" s="9"/>
       <c r="H21" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I21" s="10">
         <v>4.5199999999999996</v>
@@ -1824,7 +1824,7 @@
     </row>
     <row r="22" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A22" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B22" s="8">
         <v>5.1100000000000003</v>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="G22" s="9"/>
       <c r="H22" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I22" s="10">
         <v>4.4610000000000003</v>
@@ -1880,7 +1880,7 @@
     </row>
     <row r="23" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A23" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B23" s="8">
         <v>6.625</v>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="G23" s="9"/>
       <c r="H23" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I23" s="10">
         <v>6.0179999999999998</v>
@@ -1936,7 +1936,7 @@
     </row>
     <row r="24" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A24" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B24" s="8">
         <v>6.625</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="G24" s="9"/>
       <c r="H24" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I24" s="10">
         <v>5.9960000000000004</v>
@@ -1992,7 +1992,7 @@
     </row>
     <row r="25" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A25" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B25" s="8">
         <v>6.625</v>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="G25" s="9"/>
       <c r="H25" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I25" s="10">
         <v>5.8639999999999999</v>
@@ -2048,7 +2048,7 @@
     </row>
     <row r="26" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A26" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B26" s="8">
         <v>6.625</v>
@@ -2067,7 +2067,7 @@
       </c>
       <c r="G26" s="9"/>
       <c r="H26" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I26" s="10">
         <v>5.7439999999999998</v>
@@ -2104,7 +2104,7 @@
     </row>
     <row r="27" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A27" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B27" s="8">
         <v>6.625</v>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="G27" s="9"/>
       <c r="H27" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I27" s="10">
         <v>5.6440000000000001</v>
@@ -2160,7 +2160,7 @@
     </row>
     <row r="28" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A28" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B28" s="8">
         <v>6.625</v>
@@ -2179,7 +2179,7 @@
       </c>
       <c r="G28" s="9"/>
       <c r="H28" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I28" s="10">
         <v>5.5979999999999999</v>
@@ -2216,7 +2216,7 @@
     </row>
     <row r="29" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A29" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B29" s="8">
         <v>7</v>
@@ -2234,10 +2234,10 @@
         <v>6.25</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I29" s="10">
         <v>6.3730000000000002</v>
@@ -2274,7 +2274,7 @@
     </row>
     <row r="30" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A30" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B30" s="8">
         <v>7</v>
@@ -2293,7 +2293,7 @@
       </c>
       <c r="G30" s="9"/>
       <c r="H30" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I30" s="10">
         <v>6.3689999999999998</v>
@@ -2330,7 +2330,7 @@
     </row>
     <row r="31" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A31" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B31" s="8">
         <v>7</v>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="G31" s="9"/>
       <c r="H31" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I31" s="10">
         <v>6.3239999999999998</v>
@@ -2386,7 +2386,7 @@
     </row>
     <row r="32" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A32" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B32" s="8">
         <v>7</v>
@@ -2404,10 +2404,10 @@
         <v>6</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I32" s="10">
         <v>6.2149999999999999</v>
@@ -2444,7 +2444,7 @@
     </row>
     <row r="33" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A33" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B33" s="8">
         <v>7</v>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="G33" s="9"/>
       <c r="H33" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I33" s="10">
         <v>6.101</v>
@@ -2500,7 +2500,7 @@
     </row>
     <row r="34" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A34" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B34" s="8">
         <v>7</v>
@@ -2519,7 +2519,7 @@
       </c>
       <c r="G34" s="9"/>
       <c r="H34" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I34" s="10">
         <v>5.9749999999999996</v>
@@ -2556,7 +2556,7 @@
     </row>
     <row r="35" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A35" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B35" s="8">
         <v>7</v>
@@ -2575,7 +2575,7 @@
       </c>
       <c r="G35" s="9"/>
       <c r="H35" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I35" s="10">
         <v>5.93</v>
@@ -2612,7 +2612,7 @@
     </row>
     <row r="36" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A36" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B36" s="8">
         <v>7</v>
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G36" s="9"/>
       <c r="H36" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I36" s="10">
         <v>5.8959999999999999</v>
@@ -2668,7 +2668,7 @@
     </row>
     <row r="37" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A37" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B37" s="8">
         <v>7.625</v>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="G37" s="9"/>
       <c r="H37" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I37" s="10">
         <v>6.97</v>
@@ -2724,7 +2724,7 @@
     </row>
     <row r="38" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A38" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B38" s="8">
         <v>7.625</v>
@@ -2743,7 +2743,7 @@
       </c>
       <c r="G38" s="9"/>
       <c r="H38" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I38" s="10">
         <v>6.883</v>
@@ -2780,7 +2780,7 @@
     </row>
     <row r="39" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A39" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B39" s="8">
         <v>7.625</v>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="G39" s="9"/>
       <c r="H39" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I39" s="10">
         <v>6.83</v>
@@ -2836,7 +2836,7 @@
     </row>
     <row r="40" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A40" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B40" s="8">
         <v>7.625</v>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="G40" s="9"/>
       <c r="H40" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I40" s="10">
         <v>6.7519999999999998</v>
@@ -2892,7 +2892,7 @@
     </row>
     <row r="41" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A41" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B41" s="8">
         <v>7.625</v>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G41" s="9"/>
       <c r="H41" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I41" s="10">
         <v>6.4740000000000002</v>
@@ -2948,7 +2948,7 @@
     </row>
     <row r="42" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A42" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B42" s="8">
         <v>7.75</v>
@@ -2966,10 +2966,10 @@
         <v>6.5</v>
       </c>
       <c r="G42" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H42" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I42" s="10">
         <v>6.6349999999999998</v>
@@ -3006,7 +3006,7 @@
     </row>
     <row r="43" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A43" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B43" s="8">
         <v>8.625</v>
@@ -3024,10 +3024,10 @@
         <v>7.625</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H43" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I43" s="10">
         <v>7.8769999999999998</v>
@@ -3064,7 +3064,7 @@
     </row>
     <row r="44" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A44" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B44" s="8">
         <v>8.625</v>
@@ -3083,7 +3083,7 @@
       </c>
       <c r="G44" s="9"/>
       <c r="H44" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I44" s="10">
         <v>7.7960000000000003</v>
@@ -3120,7 +3120,7 @@
     </row>
     <row r="45" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A45" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B45" s="8">
         <v>8.625</v>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="G45" s="9"/>
       <c r="H45" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I45" s="10">
         <v>7.6959999999999997</v>
@@ -3176,7 +3176,7 @@
     </row>
     <row r="46" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A46" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B46" s="8">
         <v>8.625</v>
@@ -3195,7 +3195,7 @@
       </c>
       <c r="G46" s="9"/>
       <c r="H46" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I46" s="10">
         <v>7.6280000000000001</v>
@@ -3232,7 +3232,7 @@
     </row>
     <row r="47" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A47" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B47" s="8">
         <v>9.625</v>
@@ -3250,10 +3250,10 @@
         <v>8.75</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I47" s="10">
         <v>8.8450000000000006</v>
@@ -3290,7 +3290,7 @@
     </row>
     <row r="48" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A48" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B48" s="8">
         <v>9.625</v>
@@ -3308,10 +3308,10 @@
         <v>8.625</v>
       </c>
       <c r="G48" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H48" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I48" s="10">
         <v>8.7669999999999995</v>
@@ -3348,7 +3348,7 @@
     </row>
     <row r="49" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A49" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B49" s="8">
         <v>9.625</v>
@@ -3367,7 +3367,7 @@
       </c>
       <c r="G49" s="9"/>
       <c r="H49" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I49" s="10">
         <v>8.8520000000000003</v>
@@ -3404,7 +3404,7 @@
     </row>
     <row r="50" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A50" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B50" s="8">
         <v>9.625</v>
@@ -3422,10 +3422,10 @@
         <v>8.5</v>
       </c>
       <c r="G50" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H50" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I50" s="10">
         <v>8.7219999999999995</v>
@@ -3462,7 +3462,7 @@
     </row>
     <row r="51" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A51" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B51" s="8">
         <v>9.625</v>
@@ -3480,10 +3480,10 @@
         <v>8.375</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H51" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I51" s="10">
         <v>8.609</v>
@@ -3520,7 +3520,7 @@
     </row>
     <row r="52" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A52" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B52" s="8">
         <v>9.875</v>
@@ -3538,10 +3538,10 @@
         <v>8.5</v>
       </c>
       <c r="G52" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H52" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I52" s="10">
         <v>8.7899999999999991</v>
@@ -3578,7 +3578,7 @@
     </row>
     <row r="53" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A53" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B53" s="8">
         <v>9.875</v>
@@ -3596,10 +3596,10 @@
         <v>8.5</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H53" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I53" s="10">
         <v>8.7349999999999994</v>
@@ -3636,7 +3636,7 @@
     </row>
     <row r="54" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A54" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B54" s="8">
         <v>9.875</v>
@@ -3654,10 +3654,10 @@
         <v>8.5</v>
       </c>
       <c r="G54" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H54" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I54" s="10">
         <v>8.6959999999999997</v>
@@ -3694,7 +3694,7 @@
     </row>
     <row r="55" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A55" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B55" s="8">
         <v>10.75</v>
@@ -3712,10 +3712,10 @@
         <v>9.875</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H55" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I55" s="10">
         <v>10.118</v>
@@ -3752,7 +3752,7 @@
     </row>
     <row r="56" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A56" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B56" s="8">
         <v>10.75</v>
@@ -3771,7 +3771,7 @@
       </c>
       <c r="G56" s="9"/>
       <c r="H56" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I56" s="10">
         <v>10.028</v>
@@ -3808,7 +3808,7 @@
     </row>
     <row r="57" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A57" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B57" s="8">
         <v>10.75</v>
@@ -3826,10 +3826,10 @@
         <v>9.6999999999999993</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H57" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I57" s="10">
         <v>9.9469999999999992</v>
@@ -3866,7 +3866,7 @@
     </row>
     <row r="58" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A58" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B58" s="8">
         <v>10.75</v>
@@ -3885,7 +3885,7 @@
       </c>
       <c r="G58" s="9"/>
       <c r="H58" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I58" s="10">
         <v>9.859</v>
@@ -3922,7 +3922,7 @@
     </row>
     <row r="59" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A59" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B59" s="8">
         <v>10.75</v>
@@ -3940,10 +3940,10 @@
         <v>9.5</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H59" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I59" s="10">
         <v>9.7620000000000005</v>
@@ -3980,7 +3980,7 @@
     </row>
     <row r="60" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A60" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B60" s="8">
         <v>10.75</v>
@@ -3998,10 +3998,10 @@
         <v>9.375</v>
       </c>
       <c r="G60" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H60" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I60" s="10">
         <v>9.4429999999999996</v>
@@ -4038,7 +4038,7 @@
     </row>
     <row r="61" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A61" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B61" s="8">
         <v>10.75</v>
@@ -4056,10 +4056,10 @@
         <v>9.33</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H61" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I61" s="10">
         <v>9.3940000000000001</v>
@@ -4096,7 +4096,7 @@
     </row>
     <row r="62" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A62" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B62" s="8">
         <v>11.75</v>
@@ -4115,7 +4115,7 @@
       </c>
       <c r="G62" s="9"/>
       <c r="H62" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I62" s="10">
         <v>11.063000000000001</v>
@@ -4152,7 +4152,7 @@
     </row>
     <row r="63" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A63" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B63" s="8">
         <v>11.75</v>
@@ -4170,10 +4170,10 @@
         <v>10.625</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H63" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I63" s="10">
         <v>10.965999999999999</v>
@@ -4210,7 +4210,7 @@
     </row>
     <row r="64" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A64" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B64" s="8">
         <v>11.75</v>
@@ -4228,10 +4228,10 @@
         <v>10.625</v>
       </c>
       <c r="G64" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H64" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I64" s="10">
         <v>10.885</v>
@@ -4268,7 +4268,7 @@
     </row>
     <row r="65" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A65" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B65" s="8">
         <v>11.75</v>
@@ -4286,10 +4286,10 @@
         <v>10.5</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H65" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I65" s="10">
         <v>10.807</v>
@@ -4326,7 +4326,7 @@
     </row>
     <row r="66" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A66" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B66" s="8">
         <v>11.875</v>
@@ -4345,7 +4345,7 @@
       </c>
       <c r="G66" s="9"/>
       <c r="H66" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I66" s="10">
         <v>10.981</v>
@@ -4382,7 +4382,7 @@
     </row>
     <row r="67" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A67" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B67" s="8">
         <v>11.875</v>
@@ -4400,10 +4400,10 @@
         <v>10.625</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H67" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I67" s="10">
         <v>10.933</v>
@@ -4440,7 +4440,7 @@
     </row>
     <row r="68" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A68" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B68" s="8">
         <v>13.375</v>
@@ -4459,7 +4459,7 @@
       </c>
       <c r="G68" s="9"/>
       <c r="H68" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I68" s="10">
         <v>12.709</v>
@@ -4496,7 +4496,7 @@
     </row>
     <row r="69" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A69" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B69" s="8">
         <v>13.375</v>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="G69" s="9"/>
       <c r="H69" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I69" s="10">
         <v>12.619</v>
@@ -4552,7 +4552,7 @@
     </row>
     <row r="70" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A70" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B70" s="8">
         <v>13.375</v>
@@ -4570,10 +4570,10 @@
         <v>12.25</v>
       </c>
       <c r="G70" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H70" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I70" s="10">
         <v>12.558</v>
@@ -4610,7 +4610,7 @@
     </row>
     <row r="71" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A71" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B71" s="14">
         <v>13.375</v>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="G71" s="9"/>
       <c r="H71" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I71" s="10">
         <v>12.502000000000001</v>
@@ -4666,7 +4666,7 @@
     </row>
     <row r="72" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A72" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B72" s="8">
         <v>13.625</v>
@@ -4684,10 +4684,10 @@
         <v>12.25</v>
       </c>
       <c r="G72" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H72" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I72" s="10">
         <v>12.444000000000001</v>
@@ -4724,7 +4724,7 @@
     </row>
     <row r="73" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A73" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B73" s="8">
         <v>14</v>
@@ -4742,10 +4742,10 @@
         <v>12.75</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H73" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I73" s="10">
         <v>13.1</v>
@@ -4782,7 +4782,7 @@
     </row>
     <row r="74" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A74" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B74" s="8">
         <v>14</v>
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G74" s="9"/>
       <c r="H74" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I74" s="10">
         <v>13.031000000000001</v>
@@ -4838,7 +4838,7 @@
     </row>
     <row r="75" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A75" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B75" s="8">
         <v>14</v>
@@ -4857,7 +4857,7 @@
       </c>
       <c r="G75" s="9"/>
       <c r="H75" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I75" s="10">
         <v>12.941000000000001</v>
@@ -4894,7 +4894,7 @@
     </row>
     <row r="76" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A76" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B76" s="8">
         <v>14</v>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="G76" s="9"/>
       <c r="H76" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I76" s="10">
         <v>12.903</v>
@@ -4950,7 +4950,7 @@
     </row>
     <row r="77" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A77" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B77" s="8">
         <v>14</v>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="G77" s="9"/>
       <c r="H77" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I77" s="10">
         <v>12.85</v>
@@ -5006,7 +5006,7 @@
     </row>
     <row r="78" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A78" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B78" s="8">
         <v>14</v>
@@ -5025,7 +5025,7 @@
       </c>
       <c r="G78" s="9"/>
       <c r="H78" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I78" s="10">
         <v>12.760999999999999</v>
@@ -5062,7 +5062,7 @@
     </row>
     <row r="79" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A79" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B79" s="8">
         <v>14</v>
@@ -5080,10 +5080,10 @@
         <v>12.25</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H79" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I79" s="10">
         <v>12.670999999999999</v>
@@ -5120,7 +5120,7 @@
     </row>
     <row r="80" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A80" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B80" s="8">
         <v>14</v>
@@ -5138,10 +5138,10 @@
         <v>12.25</v>
       </c>
       <c r="G80" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H80" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I80" s="10">
         <v>12.670999999999999</v>
@@ -5178,7 +5178,7 @@
     </row>
     <row r="81" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A81" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B81" s="8">
         <v>7.625</v>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="G81" s="9"/>
       <c r="H81" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I81" s="10">
         <v>6.3090000000000002</v>
@@ -5234,7 +5234,7 @@
     </row>
     <row r="82" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A82" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B82" s="8">
         <v>7.625</v>
@@ -5253,7 +5253,7 @@
       </c>
       <c r="G82" s="9"/>
       <c r="H82" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I82" s="10">
         <v>6.1239999999999997</v>
@@ -5290,7 +5290,7 @@
     </row>
     <row r="83" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A83" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B83" s="8">
         <v>7.625</v>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="G83" s="9"/>
       <c r="H83" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I83" s="10">
         <v>5.9939999999999998</v>
@@ -5346,7 +5346,7 @@
     </row>
     <row r="84" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A84" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B84" s="8">
         <f>7+5/8</f>
@@ -5365,10 +5365,10 @@
         <v>5.875</v>
       </c>
       <c r="G84" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H84" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I84" s="10">
         <v>5.9390000000000001</v>
@@ -5405,7 +5405,7 @@
     </row>
     <row r="85" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A85" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B85" s="15">
         <f>10+1/2</f>
@@ -5424,10 +5424,10 @@
         <v>8.5</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H85" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I85" s="10">
         <v>8.6590000000000007</v>
@@ -5464,7 +5464,7 @@
     </row>
     <row r="86" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A86" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B86" s="15">
         <f t="shared" ref="B86:B87" si="0">10+1/2</f>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="G86" s="9"/>
       <c r="H86" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I86" s="10">
         <v>9.6310000000000002</v>
@@ -5521,7 +5521,7 @@
     </row>
     <row r="87" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A87" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B87" s="15">
         <f t="shared" si="0"/>
@@ -5540,10 +5540,10 @@
         <v>9.33</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H87" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I87" s="10">
         <v>9.6159999999999997</v>
@@ -5580,7 +5580,7 @@
     </row>
     <row r="88" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A88" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B88" s="15">
         <v>10.75</v>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="G88" s="9"/>
       <c r="H88" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I88" s="10">
         <v>9.3369999999999997</v>
@@ -5636,7 +5636,7 @@
     </row>
     <row r="89" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A89" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B89" s="15">
         <v>10.75</v>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="G89" s="9"/>
       <c r="H89" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I89" s="10">
         <v>9.3520000000000003</v>
@@ -5692,7 +5692,7 @@
     </row>
     <row r="90" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A90" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B90" s="15">
         <v>10.75</v>
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G90" s="9"/>
       <c r="H90" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I90" s="10">
         <v>9.0850000000000009</v>
@@ -5748,7 +5748,7 @@
     </row>
     <row r="91" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A91" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B91" s="15">
         <v>10.75</v>
@@ -5767,7 +5767,7 @@
       </c>
       <c r="G91" s="9"/>
       <c r="H91" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I91" s="10">
         <v>8.7260000000000009</v>
@@ -5802,7 +5802,7 @@
     </row>
     <row r="92" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A92" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B92" s="15">
         <v>10.75</v>
@@ -5821,7 +5821,7 @@
       </c>
       <c r="G92" s="9"/>
       <c r="H92" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I92" s="10">
         <v>8.8710000000000004</v>
@@ -5858,7 +5858,7 @@
     </row>
     <row r="93" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A93" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B93" s="15">
         <f>10+7/8</f>
@@ -5878,7 +5878,7 @@
       </c>
       <c r="G93" s="9"/>
       <c r="H93" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I93" s="10">
         <v>9.6690000000000005</v>
@@ -5913,7 +5913,7 @@
     </row>
     <row r="94" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A94" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B94" s="15">
         <f>12+1/4</f>
@@ -5933,7 +5933,7 @@
       </c>
       <c r="G94" s="9"/>
       <c r="H94" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I94" s="10">
         <v>10.085000000000001</v>
@@ -5966,7 +5966,7 @@
     </row>
     <row r="95" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A95" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B95" s="7">
         <f>2+3/8</f>
@@ -5985,10 +5985,10 @@
         <v>1.91</v>
       </c>
       <c r="G95" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H95" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I95" s="18">
         <v>1.9570000000000001</v>
@@ -6026,7 +6026,7 @@
     </row>
     <row r="96" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A96" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B96" s="7">
         <f t="shared" ref="B96:B100" si="1">2+3/8</f>
@@ -6046,7 +6046,7 @@
       </c>
       <c r="G96" s="17"/>
       <c r="H96" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I96" s="18">
         <v>1.913</v>
@@ -6084,7 +6084,7 @@
     </row>
     <row r="97" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A97" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B97" s="7">
         <f t="shared" si="1"/>
@@ -6104,7 +6104,7 @@
       </c>
       <c r="G97" s="17"/>
       <c r="H97" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I97" s="18">
         <v>1.827</v>
@@ -6142,7 +6142,7 @@
     </row>
     <row r="98" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A98" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B98" s="7">
         <f t="shared" si="1"/>
@@ -6162,7 +6162,7 @@
       </c>
       <c r="G98" s="17"/>
       <c r="H98" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I98" s="18">
         <v>1.7829999999999999</v>
@@ -6200,7 +6200,7 @@
     </row>
     <row r="99" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A99" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B99" s="7">
         <f t="shared" si="1"/>
@@ -6220,7 +6220,7 @@
       </c>
       <c r="G99" s="17"/>
       <c r="H99" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I99" s="18">
         <v>1.76</v>
@@ -6258,7 +6258,7 @@
     </row>
     <row r="100" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A100" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B100" s="7">
         <f t="shared" si="1"/>
@@ -6278,7 +6278,7 @@
       </c>
       <c r="G100" s="17"/>
       <c r="H100" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I100" s="18">
         <v>1.6930000000000001</v>
@@ -6316,7 +6316,7 @@
     </row>
     <row r="101" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A101" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B101" s="20">
         <f>2+7/8</f>
@@ -6336,7 +6336,7 @@
       </c>
       <c r="G101" s="17"/>
       <c r="H101" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I101" s="18">
         <v>2.4089999999999998</v>
@@ -6374,7 +6374,7 @@
     </row>
     <row r="102" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A102" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B102" s="20">
         <f t="shared" ref="B102:B108" si="2">2+7/8</f>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="G102" s="17"/>
       <c r="H102" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I102" s="18">
         <v>2.2709999999999999</v>
@@ -6432,7 +6432,7 @@
     </row>
     <row r="103" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A103" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B103" s="20">
         <f t="shared" si="2"/>
@@ -6452,7 +6452,7 @@
       </c>
       <c r="G103" s="17"/>
       <c r="H103" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I103" s="18">
         <v>2.2200000000000002</v>
@@ -6490,7 +6490,7 @@
     </row>
     <row r="104" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A104" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B104" s="20">
         <f t="shared" si="2"/>
@@ -6510,7 +6510,7 @@
       </c>
       <c r="G104" s="17"/>
       <c r="H104" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I104" s="18">
         <v>2.169</v>
@@ -6548,7 +6548,7 @@
     </row>
     <row r="105" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A105" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B105" s="20">
         <f t="shared" si="2"/>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="G105" s="17"/>
       <c r="H105" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I105" s="18">
         <v>2.133</v>
@@ -6606,7 +6606,7 @@
     </row>
     <row r="106" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A106" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B106" s="20">
         <f t="shared" si="2"/>
@@ -6626,7 +6626,7 @@
       </c>
       <c r="G106" s="17"/>
       <c r="H106" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I106" s="18">
         <v>2.0859999999999999</v>
@@ -6664,7 +6664,7 @@
     </row>
     <row r="107" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A107" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B107" s="20">
         <f>2+7/8</f>
@@ -6684,7 +6684,7 @@
       </c>
       <c r="G107" s="17"/>
       <c r="H107" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I107" s="18">
         <v>2.0659999999999998</v>
@@ -6722,7 +6722,7 @@
     </row>
     <row r="108" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A108" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B108" s="20">
         <f t="shared" si="2"/>
@@ -6742,7 +6742,7 @@
       </c>
       <c r="G108" s="17"/>
       <c r="H108" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I108" s="18">
         <v>1.9870000000000001</v>
@@ -6780,7 +6780,7 @@
     </row>
     <row r="109" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A109" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B109" s="20">
         <v>3.5</v>
@@ -6799,7 +6799,7 @@
       </c>
       <c r="G109" s="17"/>
       <c r="H109" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I109" s="18">
         <v>3.1040000000000001</v>
@@ -6837,7 +6837,7 @@
     </row>
     <row r="110" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A110" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B110" s="20">
         <v>3.5</v>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="G110" s="17"/>
       <c r="H110" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I110" s="18">
         <v>3.0219999999999998</v>
@@ -6894,7 +6894,7 @@
     </row>
     <row r="111" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A111" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B111" s="20">
         <v>3.5</v>
@@ -6912,10 +6912,10 @@
         <v>2.9</v>
       </c>
       <c r="G111" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H111" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I111" s="18">
         <v>2.9590000000000001</v>
@@ -6953,7 +6953,7 @@
     </row>
     <row r="112" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A112" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B112" s="20">
         <v>3.5</v>
@@ -6972,7 +6972,7 @@
       </c>
       <c r="G112" s="17"/>
       <c r="H112" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I112" s="18">
         <v>2.8940000000000001</v>
@@ -7010,7 +7010,7 @@
     </row>
     <row r="113" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A113" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B113" s="20">
         <v>3.5</v>
@@ -7029,7 +7029,7 @@
       </c>
       <c r="G113" s="17"/>
       <c r="H113" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I113" s="18">
         <v>2.7069999999999999</v>
@@ -7067,7 +7067,7 @@
     </row>
     <row r="114" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A114" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B114" s="20">
         <v>3.5</v>
@@ -7086,7 +7086,7 @@
       </c>
       <c r="G114" s="17"/>
       <c r="H114" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I114" s="18">
         <v>2.6480000000000001</v>
@@ -7124,7 +7124,7 @@
     </row>
     <row r="115" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A115" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B115" s="20">
         <v>3.5</v>
@@ -7143,7 +7143,7 @@
       </c>
       <c r="G115" s="17"/>
       <c r="H115" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I115" s="18">
         <v>2.62</v>
@@ -7181,7 +7181,7 @@
     </row>
     <row r="116" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A116" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B116" s="20">
         <v>3.5</v>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="G116" s="17"/>
       <c r="H116" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I116" s="18">
         <v>2.589</v>
@@ -7238,7 +7238,7 @@
     </row>
     <row r="117" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A117" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B117" s="20">
         <v>3.5</v>
@@ -7257,7 +7257,7 @@
       </c>
       <c r="G117" s="17"/>
       <c r="H117" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I117" s="18">
         <v>2.5179999999999998</v>
@@ -7295,7 +7295,7 @@
     </row>
     <row r="118" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A118" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B118" s="20">
         <v>3.5</v>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="G118" s="17"/>
       <c r="H118" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I118" s="18">
         <v>2.4670000000000001</v>
@@ -7352,7 +7352,7 @@
     </row>
     <row r="119" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A119" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B119" s="20">
         <v>3.5</v>
@@ -7371,7 +7371,7 @@
       </c>
       <c r="G119" s="17"/>
       <c r="H119" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I119" s="18">
         <v>2.3679999999999999</v>
@@ -7409,7 +7409,7 @@
     </row>
     <row r="120" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A120" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B120" s="20">
         <v>4</v>
@@ -7428,7 +7428,7 @@
       </c>
       <c r="G120" s="17"/>
       <c r="H120" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I120" s="18">
         <v>3.5670000000000002</v>
@@ -7466,7 +7466,7 @@
     </row>
     <row r="121" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A121" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B121" s="20">
         <v>4</v>
@@ -7485,7 +7485,7 @@
       </c>
       <c r="G121" s="17"/>
       <c r="H121" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I121" s="18">
         <v>3.5</v>
@@ -7523,7 +7523,7 @@
     </row>
     <row r="122" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A122" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B122" s="20">
         <v>4</v>
@@ -7542,7 +7542,7 @@
       </c>
       <c r="G122" s="17"/>
       <c r="H122" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I122" s="18">
         <v>3.4369999999999998</v>
@@ -7580,7 +7580,7 @@
     </row>
     <row r="123" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A123" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B123" s="20">
         <v>4</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="G123" s="17"/>
       <c r="H123" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I123" s="18">
         <v>3.3980000000000001</v>
@@ -7637,7 +7637,7 @@
     </row>
     <row r="124" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A124" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B124" s="20">
         <v>4</v>
@@ -7656,7 +7656,7 @@
       </c>
       <c r="G124" s="17"/>
       <c r="H124" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I124" s="18">
         <v>3.327</v>
@@ -7694,7 +7694,7 @@
     </row>
     <row r="125" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A125" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B125" s="20">
         <v>4</v>
@@ -7713,7 +7713,7 @@
       </c>
       <c r="G125" s="17"/>
       <c r="H125" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I125" s="18">
         <v>3.1890000000000001</v>
@@ -7751,7 +7751,7 @@
     </row>
     <row r="126" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A126" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B126" s="20">
         <v>4</v>
@@ -7770,7 +7770,7 @@
       </c>
       <c r="G126" s="17"/>
       <c r="H126" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I126" s="18">
         <v>3.13</v>
@@ -7808,7 +7808,7 @@
     </row>
     <row r="127" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A127" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B127" s="20">
         <v>4</v>
@@ -7827,7 +7827,7 @@
       </c>
       <c r="G127" s="17"/>
       <c r="H127" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I127" s="18">
         <v>3.1059999999999999</v>
@@ -7865,7 +7865,7 @@
     </row>
     <row r="128" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A128" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B128" s="20">
         <v>4</v>
@@ -7884,7 +7884,7 @@
       </c>
       <c r="G128" s="17"/>
       <c r="H128" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I128" s="18">
         <v>2.9689999999999999</v>
@@ -7922,7 +7922,7 @@
     </row>
     <row r="129" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A129" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B129" s="20">
         <v>4</v>
@@ -7941,7 +7941,7 @@
       </c>
       <c r="G129" s="17"/>
       <c r="H129" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I129" s="18">
         <v>2.7989999999999999</v>
@@ -7979,7 +7979,7 @@
     </row>
     <row r="130" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A130" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B130" s="20">
         <v>4.5</v>
@@ -7997,10 +7997,10 @@
         <v>3.95</v>
       </c>
       <c r="G130" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H130" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I130" s="18">
         <v>3.9990000000000001</v>
@@ -8038,7 +8038,7 @@
     </row>
     <row r="131" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A131" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B131" s="20">
         <v>4.5</v>
@@ -8056,10 +8056,10 @@
         <v>3.88</v>
       </c>
       <c r="G131" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H131" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I131" s="18">
         <v>3.952</v>
@@ -8097,7 +8097,7 @@
     </row>
     <row r="132" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A132" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B132" s="20">
         <v>4.5</v>
@@ -8115,10 +8115,10 @@
         <v>3.88</v>
       </c>
       <c r="G132" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H132" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I132" s="18">
         <v>3.9129999999999998</v>
@@ -8156,7 +8156,7 @@
     </row>
     <row r="133" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A133" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B133" s="20">
         <v>4.5</v>
@@ -8174,10 +8174,10 @@
         <v>3.8450000000000002</v>
       </c>
       <c r="G133" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H133" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I133" s="18">
         <v>3.8769999999999998</v>
@@ -8215,7 +8215,7 @@
     </row>
     <row r="134" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A134" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B134" s="20">
         <v>4.5</v>
@@ -8233,10 +8233,10 @@
         <v>3.75</v>
       </c>
       <c r="G134" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H134" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I134" s="18">
         <v>3.798</v>
@@ -8274,13 +8274,13 @@
     </row>
     <row r="135" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A135" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B135" s="20">
         <v>4.5</v>
       </c>
       <c r="C135" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D135" s="16">
         <v>0.38</v>
@@ -8293,7 +8293,7 @@
       </c>
       <c r="G135" s="17"/>
       <c r="H135" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I135" s="18">
         <v>3.68</v>
@@ -8331,7 +8331,7 @@
     </row>
     <row r="136" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A136" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B136" s="20">
         <v>4.5</v>
@@ -8350,7 +8350,7 @@
       </c>
       <c r="G136" s="17"/>
       <c r="H136" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I136" s="18">
         <v>3.641</v>
@@ -8388,7 +8388,7 @@
     </row>
     <row r="137" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A137" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B137" s="20">
         <v>4.5</v>
@@ -8406,10 +8406,10 @@
         <v>3.54</v>
       </c>
       <c r="G137" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H137" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I137" s="18">
         <v>3.5859999999999999</v>
@@ -8447,7 +8447,7 @@
     </row>
     <row r="138" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A138" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B138" s="20">
         <v>4.5</v>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="G138" s="17"/>
       <c r="H138" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I138" s="18">
         <v>3.444</v>
@@ -8504,7 +8504,7 @@
     </row>
     <row r="139" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A139" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B139" s="20">
         <v>4.5</v>
@@ -8523,7 +8523,7 @@
       </c>
       <c r="G139" s="17"/>
       <c r="H139" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I139" s="18">
         <v>3.35</v>
@@ -8561,7 +8561,7 @@
     </row>
     <row r="140" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A140" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B140" s="20">
         <v>5</v>
@@ -8580,7 +8580,7 @@
       </c>
       <c r="G140" s="17"/>
       <c r="H140" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I140" s="18">
         <v>4.4379999999999997</v>
@@ -8618,7 +8618,7 @@
     </row>
     <row r="141" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A141" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B141" s="20">
         <v>5</v>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="G141" s="17"/>
       <c r="H141" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I141" s="18">
         <v>4.391</v>
@@ -8675,7 +8675,7 @@
     </row>
     <row r="142" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A142" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B142" s="20">
         <v>5</v>
@@ -8694,7 +8694,7 @@
       </c>
       <c r="G142" s="17"/>
       <c r="H142" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I142" s="18">
         <v>4.391</v>
@@ -8732,7 +8732,7 @@
     </row>
     <row r="143" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A143" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B143" s="20">
         <v>5</v>
@@ -8751,7 +8751,7 @@
       </c>
       <c r="G143" s="17"/>
       <c r="H143" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I143" s="18">
         <v>4.3070000000000004</v>
@@ -8789,7 +8789,7 @@
     </row>
     <row r="144" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A144" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B144" s="20">
         <v>5</v>
@@ -8808,7 +8808,7 @@
       </c>
       <c r="G144" s="17"/>
       <c r="H144" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I144" s="18">
         <v>4.2830000000000004</v>
@@ -8846,7 +8846,7 @@
     </row>
     <row r="145" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A145" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B145" s="20">
         <v>5</v>
@@ -8865,7 +8865,7 @@
       </c>
       <c r="G145" s="17"/>
       <c r="H145" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I145" s="18">
         <v>4.2549999999999999</v>
@@ -8903,7 +8903,7 @@
     </row>
     <row r="146" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A146" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B146" s="20">
         <v>5</v>
@@ -8922,7 +8922,7 @@
       </c>
       <c r="G146" s="17"/>
       <c r="H146" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I146" s="18">
         <v>4.181</v>
@@ -8960,7 +8960,7 @@
     </row>
     <row r="147" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A147" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B147" s="20">
         <v>5</v>
@@ -8979,7 +8979,7 @@
       </c>
       <c r="G147" s="17"/>
       <c r="H147" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I147" s="18">
         <v>4.141</v>
@@ -9017,7 +9017,7 @@
     </row>
     <row r="148" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A148" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B148" s="20">
         <v>5.5</v>
@@ -9036,7 +9036,7 @@
       </c>
       <c r="G148" s="17"/>
       <c r="H148" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I148" s="18">
         <v>4.931</v>
@@ -9074,7 +9074,7 @@
     </row>
     <row r="149" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A149" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B149" s="20">
         <v>5.5</v>
@@ -9093,7 +9093,7 @@
       </c>
       <c r="G149" s="17"/>
       <c r="H149" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I149" s="18">
         <v>4.8949999999999996</v>
@@ -9131,7 +9131,7 @@
     </row>
     <row r="150" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A150" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B150" s="20">
         <v>5.5</v>
@@ -9150,7 +9150,7 @@
       </c>
       <c r="G150" s="17"/>
       <c r="H150" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I150" s="18">
         <v>4.8949999999999996</v>
@@ -9188,7 +9188,7 @@
     </row>
     <row r="151" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A151" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B151" s="20">
         <v>5.5</v>
@@ -9207,7 +9207,7 @@
       </c>
       <c r="G151" s="17"/>
       <c r="H151" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I151" s="18">
         <v>4.8949999999999996</v>
@@ -9245,7 +9245,7 @@
     </row>
     <row r="152" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A152" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B152" s="20">
         <v>5.5</v>
@@ -9264,7 +9264,7 @@
       </c>
       <c r="G152" s="17"/>
       <c r="H152" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I152" s="18">
         <v>4.8010000000000002</v>
@@ -9302,7 +9302,7 @@
     </row>
     <row r="153" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A153" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B153" s="20">
         <v>5.5</v>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="G153" s="17"/>
       <c r="H153" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I153" s="18">
         <v>4.6900000000000004</v>
@@ -9359,7 +9359,7 @@
     </row>
     <row r="154" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A154" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B154" s="20">
         <v>5.5</v>
@@ -9378,7 +9378,7 @@
       </c>
       <c r="G154" s="17"/>
       <c r="H154" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I154" s="18">
         <v>4.6470000000000002</v>
@@ -9416,7 +9416,7 @@
     </row>
     <row r="155" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A155" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B155" s="20">
         <v>5.5</v>
@@ -9435,7 +9435,7 @@
       </c>
       <c r="G155" s="17"/>
       <c r="H155" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I155" s="18">
         <v>4.5940000000000003</v>
@@ -9473,7 +9473,7 @@
     </row>
     <row r="156" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A156" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B156" s="20">
         <v>5.5</v>
@@ -9492,7 +9492,7 @@
       </c>
       <c r="G156" s="17"/>
       <c r="H156" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I156" s="18">
         <v>4.5350000000000001</v>
@@ -9530,7 +9530,7 @@
     </row>
     <row r="157" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A157" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B157" s="20">
         <v>5.75</v>
@@ -9549,7 +9549,7 @@
       </c>
       <c r="G157" s="17"/>
       <c r="H157" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I157" s="18">
         <v>5.173</v>
@@ -9587,7 +9587,7 @@
     </row>
     <row r="158" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A158" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B158" s="20">
         <v>5.75</v>
@@ -9606,7 +9606,7 @@
       </c>
       <c r="G158" s="17"/>
       <c r="H158" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I158" s="18">
         <v>5.1369999999999996</v>
@@ -9644,7 +9644,7 @@
     </row>
     <row r="159" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A159" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B159" s="20">
         <v>5.75</v>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="G159" s="17"/>
       <c r="H159" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I159" s="18">
         <v>5.09</v>
@@ -9701,7 +9701,7 @@
     </row>
     <row r="160" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A160" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B160" s="20">
         <f>6+5/8</f>
@@ -9721,7 +9721,7 @@
       </c>
       <c r="G160" s="17"/>
       <c r="H160" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I160" s="18">
         <v>6.0490000000000004</v>
@@ -9759,7 +9759,7 @@
     </row>
     <row r="161" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A161" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B161" s="20">
         <f t="shared" ref="B161:B165" si="3">6+5/8</f>
@@ -9779,7 +9779,7 @@
       </c>
       <c r="G161" s="17"/>
       <c r="H161" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I161" s="18">
         <v>6.0490000000000004</v>
@@ -9817,7 +9817,7 @@
     </row>
     <row r="162" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A162" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B162" s="20">
         <f t="shared" si="3"/>
@@ -9837,7 +9837,7 @@
       </c>
       <c r="G162" s="17"/>
       <c r="H162" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I162" s="18">
         <v>6.0490000000000004</v>
@@ -9875,7 +9875,7 @@
     </row>
     <row r="163" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A163" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B163" s="20">
         <f t="shared" si="3"/>
@@ -9895,7 +9895,7 @@
       </c>
       <c r="G163" s="17"/>
       <c r="H163" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I163" s="18">
         <v>5.931</v>
@@ -9933,7 +9933,7 @@
     </row>
     <row r="164" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A164" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B164" s="20">
         <f t="shared" si="3"/>
@@ -9953,7 +9953,7 @@
       </c>
       <c r="G164" s="17"/>
       <c r="H164" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I164" s="18">
         <v>5.8239999999999998</v>
@@ -9991,7 +9991,7 @@
     </row>
     <row r="165" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A165" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B165" s="20">
         <f t="shared" si="3"/>
@@ -10011,7 +10011,7 @@
       </c>
       <c r="G165" s="17"/>
       <c r="H165" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I165" s="18">
         <v>5.6689999999999996</v>
@@ -10049,7 +10049,7 @@
     </row>
     <row r="166" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A166" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B166" s="20">
         <v>7</v>
@@ -10067,10 +10067,10 @@
         <v>6.25</v>
       </c>
       <c r="G166" s="17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H166" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I166" s="18">
         <v>6.3239999999999998</v>
@@ -10108,7 +10108,7 @@
     </row>
     <row r="167" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A167" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B167" s="20">
         <v>7</v>
@@ -10127,7 +10127,7 @@
       </c>
       <c r="G167" s="17"/>
       <c r="H167" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I167" s="18">
         <v>6.3239999999999998</v>
@@ -10165,7 +10165,7 @@
     </row>
     <row r="168" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A168" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B168" s="20">
         <v>7</v>
@@ -10184,7 +10184,7 @@
       </c>
       <c r="G168" s="17"/>
       <c r="H168" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I168" s="18">
         <v>6.3239999999999998</v>
@@ -10222,7 +10222,7 @@
     </row>
     <row r="169" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A169" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B169" s="20">
         <v>7</v>
@@ -10240,10 +10240,10 @@
         <v>6</v>
       </c>
       <c r="G169" s="17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H169" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I169" s="18">
         <v>6.242</v>
@@ -10281,7 +10281,7 @@
     </row>
     <row r="170" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A170" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B170" s="20">
         <v>7</v>
@@ -10300,7 +10300,7 @@
       </c>
       <c r="G170" s="17"/>
       <c r="H170" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I170" s="18">
         <v>6.1609999999999996</v>
@@ -10338,7 +10338,7 @@
     </row>
     <row r="171" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A171" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B171" s="20">
         <v>7</v>
@@ -10357,7 +10357,7 @@
       </c>
       <c r="G171" s="17"/>
       <c r="H171" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I171" s="18">
         <v>6.0860000000000003</v>
@@ -10395,7 +10395,7 @@
     </row>
     <row r="172" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A172" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B172" s="20">
         <v>7</v>
@@ -10414,7 +10414,7 @@
       </c>
       <c r="G172" s="17"/>
       <c r="H172" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I172" s="18">
         <v>5.9960000000000004</v>
@@ -10452,7 +10452,7 @@
     </row>
     <row r="173" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A173" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B173" s="20">
         <v>7</v>
@@ -10471,7 +10471,7 @@
       </c>
       <c r="G173" s="17"/>
       <c r="H173" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I173" s="18">
         <v>5.9329999999999998</v>
@@ -10509,7 +10509,7 @@
     </row>
     <row r="174" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A174" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B174" s="20">
         <f>7+5/8</f>
@@ -10529,7 +10529,7 @@
       </c>
       <c r="G174" s="17"/>
       <c r="H174" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I174" s="18">
         <v>6.9189999999999996</v>
@@ -10567,7 +10567,7 @@
     </row>
     <row r="175" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A175" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B175" s="20">
         <f t="shared" ref="B175:B181" si="4">7+5/8</f>
@@ -10587,7 +10587,7 @@
       </c>
       <c r="G175" s="17"/>
       <c r="H175" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I175" s="18">
         <v>6.9189999999999996</v>
@@ -10625,7 +10625,7 @@
     </row>
     <row r="176" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A176" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B176" s="20">
         <f t="shared" si="4"/>
@@ -10645,7 +10645,7 @@
       </c>
       <c r="G176" s="17"/>
       <c r="H176" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I176" s="18">
         <v>6.9189999999999996</v>
@@ -10683,7 +10683,7 @@
     </row>
     <row r="177" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A177" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B177" s="20">
         <f t="shared" si="4"/>
@@ -10703,7 +10703,7 @@
       </c>
       <c r="G177" s="17"/>
       <c r="H177" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I177" s="18">
         <v>6.8559999999999999</v>
@@ -10741,7 +10741,7 @@
     </row>
     <row r="178" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A178" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B178" s="20">
         <f t="shared" si="4"/>
@@ -10761,7 +10761,7 @@
       </c>
       <c r="G178" s="17"/>
       <c r="H178" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I178" s="18">
         <v>6.7930000000000001</v>
@@ -10799,7 +10799,7 @@
     </row>
     <row r="179" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A179" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B179" s="20">
         <f t="shared" si="4"/>
@@ -10819,7 +10819,7 @@
       </c>
       <c r="G179" s="17"/>
       <c r="H179" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I179" s="18">
         <v>6.6829999999999998</v>
@@ -10857,7 +10857,7 @@
     </row>
     <row r="180" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A180" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B180" s="20">
         <f t="shared" si="4"/>
@@ -10877,7 +10877,7 @@
       </c>
       <c r="G180" s="17"/>
       <c r="H180" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I180" s="18">
         <v>6.6219999999999999</v>
@@ -10915,7 +10915,7 @@
     </row>
     <row r="181" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A181" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B181" s="20">
         <f t="shared" si="4"/>
@@ -10935,7 +10935,7 @@
       </c>
       <c r="G181" s="17"/>
       <c r="H181" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I181" s="18">
         <v>6.5659999999999998</v>
@@ -10973,7 +10973,7 @@
     </row>
     <row r="182" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A182" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B182" s="20">
         <v>7.75</v>
@@ -10991,10 +10991,10 @@
         <v>6.5</v>
       </c>
       <c r="G182" s="17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H182" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I182" s="18">
         <v>6.75</v>
@@ -11032,7 +11032,7 @@
     </row>
     <row r="183" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A183" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B183" s="20">
         <f>8+5/8</f>
@@ -11052,7 +11052,7 @@
       </c>
       <c r="G183" s="17"/>
       <c r="H183" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I183" s="18">
         <v>7.98</v>
@@ -11090,7 +11090,7 @@
     </row>
     <row r="184" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A184" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B184" s="20">
         <f t="shared" ref="B184:B187" si="5">8+5/8</f>
@@ -11109,10 +11109,10 @@
         <v>7.625</v>
       </c>
       <c r="G184" s="17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H184" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I184" s="18">
         <v>7.8890000000000002</v>
@@ -11150,7 +11150,7 @@
     </row>
     <row r="185" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A185" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B185" s="20">
         <f t="shared" si="5"/>
@@ -11170,7 +11170,7 @@
       </c>
       <c r="G185" s="17"/>
       <c r="H185" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I185" s="18">
         <v>7.7990000000000004</v>
@@ -11208,7 +11208,7 @@
     </row>
     <row r="186" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A186" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B186" s="20">
         <f t="shared" si="5"/>
@@ -11228,7 +11228,7 @@
       </c>
       <c r="G186" s="17"/>
       <c r="H186" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I186" s="18">
         <v>7.6959999999999997</v>
@@ -11266,7 +11266,7 @@
     </row>
     <row r="187" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A187" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B187" s="20">
         <f t="shared" si="5"/>
@@ -11286,7 +11286,7 @@
       </c>
       <c r="G187" s="17"/>
       <c r="H187" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I187" s="18">
         <v>7.6289999999999996</v>
@@ -11324,7 +11324,7 @@
     </row>
     <row r="188" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A188" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B188" s="20">
         <f>9+5/8</f>
@@ -11344,7 +11344,7 @@
       </c>
       <c r="G188" s="17"/>
       <c r="H188" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I188" s="18">
         <v>8.9979999999999993</v>
@@ -11382,7 +11382,7 @@
     </row>
     <row r="189" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A189" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B189" s="20">
         <f t="shared" ref="B189:B196" si="6">9+5/8</f>
@@ -11401,10 +11401,10 @@
         <v>8.75</v>
       </c>
       <c r="G189" s="17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H189" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I189" s="18">
         <v>8.9979999999999993</v>
@@ -11442,7 +11442,7 @@
     </row>
     <row r="190" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A190" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B190" s="20">
         <f t="shared" si="6"/>
@@ -11462,7 +11462,7 @@
       </c>
       <c r="G190" s="17"/>
       <c r="H190" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I190" s="18">
         <v>8.7650000000000006</v>
@@ -11500,7 +11500,7 @@
     </row>
     <row r="191" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A191" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B191" s="20">
         <f t="shared" si="6"/>
@@ -11520,7 +11520,7 @@
       </c>
       <c r="G191" s="17"/>
       <c r="H191" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I191" s="18">
         <v>8.9250000000000007</v>
@@ -11558,7 +11558,7 @@
     </row>
     <row r="192" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A192" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B192" s="20">
         <f t="shared" si="6"/>
@@ -11578,7 +11578,7 @@
       </c>
       <c r="G192" s="17"/>
       <c r="H192" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I192" s="18">
         <v>8.69</v>
@@ -11616,7 +11616,7 @@
     </row>
     <row r="193" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A193" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B193" s="20">
         <f t="shared" si="6"/>
@@ -11636,7 +11636,7 @@
       </c>
       <c r="G193" s="17"/>
       <c r="H193" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I193" s="18">
         <v>8.8580000000000005</v>
@@ -11674,7 +11674,7 @@
     </row>
     <row r="194" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A194" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B194" s="20">
         <f t="shared" si="6"/>
@@ -11693,10 +11693,10 @@
         <v>8.5</v>
       </c>
       <c r="G194" s="17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H194" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I194" s="18">
         <v>8.5449999999999999</v>
@@ -11734,7 +11734,7 @@
     </row>
     <row r="195" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A195" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B195" s="20">
         <f t="shared" si="6"/>
@@ -11753,10 +11753,10 @@
         <v>8.5</v>
       </c>
       <c r="G195" s="17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H195" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I195" s="18">
         <v>8.7260000000000009</v>
@@ -11794,7 +11794,7 @@
     </row>
     <row r="196" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A196" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B196" s="20">
         <f t="shared" si="6"/>
@@ -11813,10 +11813,10 @@
         <v>8.375</v>
       </c>
       <c r="G196" s="17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H196" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I196" s="18">
         <v>8.6370000000000005</v>
@@ -11854,7 +11854,7 @@
     </row>
     <row r="197" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A197" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B197" s="20">
         <f>9+7/8</f>
@@ -11873,10 +11873,10 @@
         <v>8.5</v>
       </c>
       <c r="G197" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H197" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I197" s="18">
         <v>8.8339999999999996</v>
@@ -11910,7 +11910,7 @@
     </row>
     <row r="198" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A198" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B198" s="20">
         <f t="shared" ref="B198:B199" si="7">9+7/8</f>
@@ -11930,7 +11930,7 @@
       </c>
       <c r="G198" s="17"/>
       <c r="H198" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I198" s="18">
         <v>8.6999999999999993</v>
@@ -11968,7 +11968,7 @@
     </row>
     <row r="199" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A199" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B199" s="20">
         <f t="shared" si="7"/>
@@ -11988,7 +11988,7 @@
       </c>
       <c r="G199" s="17"/>
       <c r="H199" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I199" s="18">
         <v>8.6630000000000003</v>
@@ -12026,7 +12026,7 @@
     </row>
     <row r="200" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A200" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B200" s="20">
         <f>9+7/8</f>
@@ -12046,7 +12046,7 @@
       </c>
       <c r="G200" s="17"/>
       <c r="H200" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I200" s="18">
         <v>8.6549999999999994</v>
@@ -12084,7 +12084,7 @@
     </row>
     <row r="201" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A201" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B201" s="20">
         <v>10</v>
@@ -12103,7 +12103,7 @@
       </c>
       <c r="G201" s="17"/>
       <c r="H201" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I201" s="18">
         <v>8.8659999999999997</v>
@@ -12141,7 +12141,7 @@
     </row>
     <row r="202" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A202" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B202" s="20">
         <v>10</v>
@@ -12160,7 +12160,7 @@
       </c>
       <c r="G202" s="17"/>
       <c r="H202" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I202" s="18">
         <v>8.7769999999999992</v>
@@ -12198,7 +12198,7 @@
     </row>
     <row r="203" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A203" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B203" s="20">
         <v>10.75</v>
@@ -12216,10 +12216,10 @@
         <v>9.875</v>
       </c>
       <c r="G203" s="17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H203" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I203" s="18">
         <v>10.122</v>
@@ -12257,7 +12257,7 @@
     </row>
     <row r="204" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A204" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B204" s="20">
         <v>10.75</v>
@@ -12276,7 +12276,7 @@
       </c>
       <c r="G204" s="17"/>
       <c r="H204" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I204" s="18">
         <v>10.031000000000001</v>
@@ -12314,7 +12314,7 @@
     </row>
     <row r="205" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A205" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B205" s="20">
         <v>10.75</v>
@@ -12332,10 +12332,10 @@
         <v>9.625</v>
       </c>
       <c r="G205" s="17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H205" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I205" s="18">
         <v>9.7710000000000008</v>
@@ -12373,7 +12373,7 @@
     </row>
     <row r="206" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A206" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B206" s="20">
         <v>10.75</v>
@@ -12391,10 +12391,10 @@
         <v>9.625</v>
       </c>
       <c r="G206" s="17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H206" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I206" s="18">
         <v>9.9499999999999993</v>
@@ -12432,7 +12432,7 @@
     </row>
     <row r="207" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A207" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B207" s="20">
         <v>10.75</v>
@@ -12451,7 +12451,7 @@
       </c>
       <c r="G207" s="17"/>
       <c r="H207" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I207" s="18">
         <v>9.6690000000000005</v>
@@ -12489,7 +12489,7 @@
     </row>
     <row r="208" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A208" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B208" s="20">
         <v>10.75</v>
@@ -12508,7 +12508,7 @@
       </c>
       <c r="G208" s="17"/>
       <c r="H208" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I208" s="18">
         <v>9.8620000000000001</v>
@@ -12546,7 +12546,7 @@
     </row>
     <row r="209" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A209" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B209" s="20">
         <v>10.75</v>
@@ -12564,10 +12564,10 @@
         <v>9.5</v>
       </c>
       <c r="G209" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H209" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I209" s="18">
         <v>9.57</v>
@@ -12605,7 +12605,7 @@
     </row>
     <row r="210" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A210" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B210" s="20">
         <v>10.75</v>
@@ -12624,7 +12624,7 @@
       </c>
       <c r="G210" s="17"/>
       <c r="H210" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I210" s="18">
         <v>9.7710000000000008</v>
@@ -12662,7 +12662,7 @@
     </row>
     <row r="211" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A211" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B211" s="20">
         <v>10.75</v>
@@ -12680,10 +12680,10 @@
         <v>9.375</v>
       </c>
       <c r="G211" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H211" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I211" s="18">
         <v>9.4760000000000009</v>
@@ -12721,7 +12721,7 @@
     </row>
     <row r="212" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A212" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B212" s="20">
         <v>10.75</v>
@@ -12740,7 +12740,7 @@
       </c>
       <c r="G212" s="17"/>
       <c r="H212" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I212" s="18">
         <v>9.6709999999999994</v>
@@ -12778,7 +12778,7 @@
     </row>
     <row r="213" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A213" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B213" s="20">
         <v>10.75</v>
@@ -12797,7 +12797,7 @@
       </c>
       <c r="G213" s="17"/>
       <c r="H213" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I213" s="18">
         <v>9.6310000000000002</v>
@@ -12835,7 +12835,7 @@
     </row>
     <row r="214" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A214" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B214" s="20">
         <v>11.75</v>
@@ -12854,7 +12854,7 @@
       </c>
       <c r="G214" s="17"/>
       <c r="H214" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I214" s="18">
         <v>11.066000000000001</v>
@@ -12892,7 +12892,7 @@
     </row>
     <row r="215" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A215" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B215" s="20">
         <v>11.75</v>
@@ -12910,10 +12910,10 @@
         <v>10.625</v>
       </c>
       <c r="G215" s="17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H215" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I215" s="18">
         <v>10.97</v>
@@ -12951,7 +12951,7 @@
     </row>
     <row r="216" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A216" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B216" s="20">
         <v>11.75</v>
@@ -12969,10 +12969,10 @@
         <v>10.625</v>
       </c>
       <c r="G216" s="17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H216" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I216" s="18">
         <v>10.888999999999999</v>
@@ -13010,7 +13010,7 @@
     </row>
     <row r="217" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A217" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B217" s="20">
         <v>11.75</v>
@@ -13029,7 +13029,7 @@
       </c>
       <c r="G217" s="17"/>
       <c r="H217" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I217" s="18">
         <v>10.803000000000001</v>
@@ -13067,7 +13067,7 @@
     </row>
     <row r="218" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A218" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B218" s="20">
         <f>11+7/8</f>
@@ -13087,7 +13087,7 @@
       </c>
       <c r="G218" s="17"/>
       <c r="H218" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I218" s="18">
         <v>10.986000000000001</v>
@@ -13125,7 +13125,7 @@
     </row>
     <row r="219" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A219" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B219" s="20">
         <f>13+3/8</f>
@@ -13145,7 +13145,7 @@
       </c>
       <c r="G219" s="17"/>
       <c r="H219" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I219" s="18">
         <v>12.561</v>
@@ -13183,7 +13183,7 @@
     </row>
     <row r="220" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A220" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B220" s="20">
         <f t="shared" ref="B220:B225" si="8">13+3/8</f>
@@ -13203,7 +13203,7 @@
       </c>
       <c r="G220" s="17"/>
       <c r="H220" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I220" s="18">
         <v>12.714</v>
@@ -13241,7 +13241,7 @@
     </row>
     <row r="221" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A221" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B221" s="20">
         <f t="shared" si="8"/>
@@ -13261,7 +13261,7 @@
       </c>
       <c r="G221" s="17"/>
       <c r="H221" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I221" s="18">
         <v>12.624000000000001</v>
@@ -13299,7 +13299,7 @@
     </row>
     <row r="222" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A222" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B222" s="20">
         <f t="shared" si="8"/>
@@ -13318,10 +13318,10 @@
         <v>12.25</v>
       </c>
       <c r="G222" s="17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H222" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I222" s="18">
         <v>12.561999999999999</v>
@@ -13359,7 +13359,7 @@
     </row>
     <row r="223" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A223" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B223" s="20">
         <f t="shared" si="8"/>
@@ -13379,7 +13379,7 @@
       </c>
       <c r="G223" s="17"/>
       <c r="H223" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I223" s="18">
         <v>12.497999999999999</v>
@@ -13417,7 +13417,7 @@
     </row>
     <row r="224" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A224" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B224" s="20">
         <f t="shared" si="8"/>
@@ -13437,7 +13437,7 @@
       </c>
       <c r="G224" s="17"/>
       <c r="H224" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I224" s="18">
         <v>12.442</v>
@@ -13475,7 +13475,7 @@
     </row>
     <row r="225" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A225" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B225" s="20">
         <f t="shared" si="8"/>
@@ -13495,7 +13495,7 @@
       </c>
       <c r="G225" s="17"/>
       <c r="H225" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I225" s="18">
         <v>12.393000000000001</v>
@@ -13533,7 +13533,7 @@
     </row>
     <row r="226" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A226" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B226" s="20">
         <v>13.625</v>
@@ -13551,10 +13551,10 @@
         <v>12.25</v>
       </c>
       <c r="G226" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H226" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I226" s="18">
         <v>12.614000000000001</v>
@@ -13592,7 +13592,7 @@
     </row>
     <row r="227" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A227" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B227" s="20">
         <v>14</v>
@@ -13611,7 +13611,7 @@
       </c>
       <c r="G227" s="17"/>
       <c r="H227" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I227" s="18">
         <v>13.096</v>
@@ -13649,7 +13649,7 @@
     </row>
     <row r="228" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A228" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B228" s="20">
         <v>14</v>
@@ -13668,7 +13668,7 @@
       </c>
       <c r="G228" s="17"/>
       <c r="H228" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I228" s="18">
         <v>13.026999999999999</v>
@@ -13706,7 +13706,7 @@
     </row>
     <row r="229" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A229" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B229" s="20">
         <v>14</v>
@@ -13725,7 +13725,7 @@
       </c>
       <c r="G229" s="17"/>
       <c r="H229" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I229" s="18">
         <v>12.936999999999999</v>
@@ -13763,7 +13763,7 @@
     </row>
     <row r="230" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A230" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B230" s="20">
         <v>14</v>
@@ -13782,7 +13782,7 @@
       </c>
       <c r="G230" s="17"/>
       <c r="H230" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I230" s="18">
         <v>12.898999999999999</v>
@@ -13820,7 +13820,7 @@
     </row>
     <row r="231" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A231" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B231" s="20">
         <v>14</v>
@@ -13839,7 +13839,7 @@
       </c>
       <c r="G231" s="17"/>
       <c r="H231" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I231" s="18">
         <v>12.846</v>
@@ -13877,7 +13877,7 @@
     </row>
     <row r="232" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A232" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B232" s="20">
         <v>14</v>
@@ -13896,7 +13896,7 @@
       </c>
       <c r="G232" s="17"/>
       <c r="H232" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I232" s="18">
         <v>12.757</v>
@@ -13934,7 +13934,7 @@
     </row>
     <row r="233" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A233" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B233" s="20">
         <v>14</v>
@@ -13952,10 +13952,10 @@
         <v>12.25</v>
       </c>
       <c r="G233" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H233" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I233" s="18">
         <v>12.667</v>
@@ -13993,7 +13993,7 @@
     </row>
     <row r="234" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A234" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B234" s="20">
         <v>15</v>
@@ -14012,7 +14012,7 @@
       </c>
       <c r="G234" s="17"/>
       <c r="H234" s="16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I234" s="18">
         <v>14.076000000000001</v>
@@ -14050,7 +14050,7 @@
     </row>
     <row r="235" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A235" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B235" s="20">
         <v>16</v>
@@ -14069,7 +14069,7 @@
       </c>
       <c r="G235" s="17"/>
       <c r="H235" s="16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I235" s="18">
         <v>15.233000000000001</v>
@@ -14107,7 +14107,7 @@
     </row>
     <row r="236" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A236" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B236" s="20">
         <v>16</v>
@@ -14126,7 +14126,7 @@
       </c>
       <c r="G236" s="17"/>
       <c r="H236" s="16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I236" s="18">
         <v>15.106999999999999</v>
@@ -14164,7 +14164,7 @@
     </row>
     <row r="237" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A237" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B237" s="20">
         <v>16</v>
@@ -14183,7 +14183,7 @@
       </c>
       <c r="G237" s="17"/>
       <c r="H237" s="16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I237" s="18">
         <v>14.946</v>
@@ -14217,7 +14217,7 @@
     </row>
     <row r="238" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A238" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B238" s="16">
         <f>18+5/8</f>
@@ -14237,7 +14237,7 @@
       </c>
       <c r="G238" s="17"/>
       <c r="H238" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I238" s="18">
         <v>17.817</v>
@@ -14279,7 +14279,7 @@
     </row>
     <row r="239" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A239" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B239" s="16">
         <f t="shared" ref="B239:B245" si="9">18+5/8</f>
@@ -14298,10 +14298,10 @@
         <v>17.5</v>
       </c>
       <c r="G239" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H239" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I239" s="18">
         <v>17.731000000000002</v>
@@ -14343,7 +14343,7 @@
     </row>
     <row r="240" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A240" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B240" s="16">
         <f t="shared" si="9"/>
@@ -14363,7 +14363,7 @@
       </c>
       <c r="G240" s="17"/>
       <c r="H240" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I240" s="18">
         <v>17.568000000000001</v>
@@ -14405,7 +14405,7 @@
     </row>
     <row r="241" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A241" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B241" s="16">
         <f t="shared" si="9"/>
@@ -14425,7 +14425,7 @@
       </c>
       <c r="G241" s="17"/>
       <c r="H241" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I241" s="18">
         <v>17.54</v>
@@ -14467,7 +14467,7 @@
     </row>
     <row r="242" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A242" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B242" s="16">
         <f t="shared" si="9"/>
@@ -14487,7 +14487,7 @@
       </c>
       <c r="G242" s="17"/>
       <c r="H242" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I242" s="18">
         <v>17.492999999999999</v>
@@ -14529,7 +14529,7 @@
     </row>
     <row r="243" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A243" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B243" s="16">
         <f t="shared" si="9"/>
@@ -14549,7 +14549,7 @@
       </c>
       <c r="G243" s="17"/>
       <c r="H243" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I243" s="18">
         <v>17.431000000000001</v>
@@ -14591,7 +14591,7 @@
     </row>
     <row r="244" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A244" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B244" s="16">
         <f t="shared" si="9"/>
@@ -14611,7 +14611,7 @@
       </c>
       <c r="G244" s="17"/>
       <c r="H244" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I244" s="18">
         <v>17.396000000000001</v>
@@ -14653,7 +14653,7 @@
     </row>
     <row r="245" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A245" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B245" s="16">
         <f t="shared" si="9"/>
@@ -14673,7 +14673,7 @@
       </c>
       <c r="G245" s="17"/>
       <c r="H245" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I245" s="18">
         <v>17.353000000000002</v>
@@ -14715,7 +14715,7 @@
     </row>
     <row r="246" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A246" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B246" s="16">
         <v>20</v>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="G246" s="17"/>
       <c r="H246" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I246" s="18">
         <v>19.187000000000001</v>
@@ -14776,7 +14776,7 @@
     </row>
     <row r="247" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A247" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B247" s="16">
         <v>20</v>
@@ -14795,7 +14795,7 @@
       </c>
       <c r="G247" s="17"/>
       <c r="H247" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I247" s="18">
         <v>19.079000000000001</v>
@@ -14837,7 +14837,7 @@
     </row>
     <row r="248" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A248" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B248" s="16">
         <v>20</v>
@@ -14856,7 +14856,7 @@
       </c>
       <c r="G248" s="17"/>
       <c r="H248" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I248" s="18">
         <v>18.846</v>
@@ -14898,7 +14898,7 @@
     </row>
     <row r="249" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A249" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B249" s="16">
         <v>20</v>
@@ -14917,7 +14917,7 @@
       </c>
       <c r="G249" s="17"/>
       <c r="H249" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I249" s="18">
         <v>18.899999999999999</v>
@@ -14959,7 +14959,7 @@
     </row>
     <row r="250" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A250" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B250" s="16">
         <v>20</v>
@@ -14978,7 +14978,7 @@
       </c>
       <c r="G250" s="17"/>
       <c r="H250" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I250" s="18">
         <v>18.829000000000001</v>
@@ -15020,7 +15020,7 @@
     </row>
     <row r="251" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A251" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B251" s="20">
         <v>7.75</v>
@@ -15039,7 +15039,7 @@
       </c>
       <c r="G251" s="17"/>
       <c r="H251" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I251" s="18">
         <v>6.5389999999999997</v>
@@ -15069,7 +15069,7 @@
     </row>
     <row r="252" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A252" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B252" s="20">
         <f>9+5/8</f>
@@ -15088,10 +15088,10 @@
         <v>8.5</v>
       </c>
       <c r="G252" s="17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H252" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I252" s="18">
         <v>8.5350000000000001</v>
@@ -15127,7 +15127,7 @@
     </row>
     <row r="253" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A253" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B253" s="20">
         <f>9+7/8</f>
@@ -15146,10 +15146,10 @@
         <v>8.5</v>
       </c>
       <c r="G253" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H253" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I253" s="18">
         <v>8.5359999999999996</v>
@@ -15187,7 +15187,7 @@
     </row>
     <row r="254" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A254" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B254" s="20">
         <f t="shared" ref="B254:B255" si="10">9+7/8</f>
@@ -15206,10 +15206,10 @@
         <v>8.5</v>
       </c>
       <c r="G254" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H254" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I254" s="18">
         <v>8.5359999999999996</v>
@@ -15243,7 +15243,7 @@
     </row>
     <row r="255" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A255" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B255" s="20">
         <f t="shared" si="10"/>
@@ -15262,10 +15262,10 @@
         <v>8.5</v>
       </c>
       <c r="G255" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H255" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I255" s="18">
         <v>8.5359999999999996</v>
@@ -15299,7 +15299,7 @@
     </row>
     <row r="256" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A256" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B256" s="20">
         <v>10</v>
@@ -15318,7 +15318,7 @@
       </c>
       <c r="G256" s="17"/>
       <c r="H256" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I256" s="18">
         <v>8.5359999999999996</v>
@@ -15352,7 +15352,7 @@
     </row>
     <row r="257" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A257" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B257" s="20">
         <v>10</v>
@@ -15370,10 +15370,10 @@
         <v>8.5</v>
       </c>
       <c r="G257" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H257" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I257" s="18">
         <v>8.5359999999999996</v>
@@ -15407,7 +15407,7 @@
     </row>
     <row r="258" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A258" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B258" s="20">
         <v>10.175000000000001</v>
@@ -15425,10 +15425,10 @@
         <v>8.5</v>
       </c>
       <c r="G258" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H258" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I258" s="18">
         <v>8.5359999999999996</v>
@@ -15458,7 +15458,7 @@
     </row>
     <row r="259" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A259" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B259" s="20">
         <v>10.75</v>
@@ -15477,7 +15477,7 @@
       </c>
       <c r="G259" s="17"/>
       <c r="H259" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I259" s="18">
         <v>9.5389999999999997</v>
@@ -15513,7 +15513,7 @@
     </row>
     <row r="260" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A260" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B260" s="20">
         <v>10.75</v>
@@ -15531,10 +15531,10 @@
         <v>9.5</v>
       </c>
       <c r="G260" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H260" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I260" s="18">
         <v>9.5359999999999996</v>
@@ -15570,7 +15570,7 @@
     </row>
     <row r="261" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A261" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B261" s="20">
         <v>10.75</v>
@@ -15589,7 +15589,7 @@
       </c>
       <c r="G261" s="17"/>
       <c r="H261" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I261" s="18">
         <v>9.0359999999999996</v>
@@ -15623,7 +15623,7 @@
     </row>
     <row r="262" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A262" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B262" s="20">
         <f>10+7/8</f>
@@ -15642,10 +15642,10 @@
         <v>9.5</v>
       </c>
       <c r="G262" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H262" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I262" s="18">
         <v>9.5359999999999996</v>
@@ -15679,7 +15679,7 @@
     </row>
     <row r="263" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A263" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B263" s="20">
         <v>11.75</v>
@@ -15697,10 +15697,10 @@
         <v>10.625</v>
       </c>
       <c r="G263" s="17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H263" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I263" s="18">
         <v>10.661</v>
@@ -15736,7 +15736,7 @@
     </row>
     <row r="264" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A264" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B264" s="20">
         <v>11.75</v>
@@ -15754,10 +15754,10 @@
         <v>10.625</v>
       </c>
       <c r="G264" s="17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H264" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I264" s="18">
         <v>10.661</v>
@@ -15793,7 +15793,7 @@
     </row>
     <row r="265" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A265" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B265" s="20">
         <f>11+7/8</f>
@@ -15812,10 +15812,10 @@
         <v>10.625</v>
       </c>
       <c r="G265" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H265" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I265" s="18">
         <v>10.661</v>
@@ -15851,7 +15851,7 @@
     </row>
     <row r="266" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A266" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B266" s="20">
         <f>13+5/8</f>
@@ -15870,10 +15870,10 @@
         <v>12.25</v>
       </c>
       <c r="G266" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H266" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I266" s="18">
         <v>12.287000000000001</v>
@@ -15909,7 +15909,7 @@
     </row>
     <row r="267" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A267" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B267" s="20">
         <f>13+3/4</f>
@@ -15928,10 +15928,10 @@
         <v>12.25</v>
       </c>
       <c r="G267" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H267" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I267" s="18">
         <v>12.286</v>
@@ -15961,7 +15961,7 @@
     </row>
     <row r="268" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A268" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B268" s="20">
         <f>13+7/8</f>
@@ -15980,10 +15980,10 @@
         <v>12.259</v>
       </c>
       <c r="G268" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H268" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I268" s="18">
         <v>12.286</v>
@@ -16013,7 +16013,7 @@
     </row>
     <row r="269" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A269" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B269" s="20">
         <v>14</v>
@@ -16031,10 +16031,10 @@
         <v>12.25</v>
       </c>
       <c r="G269" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H269" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I269" s="18">
         <v>12.284000000000001</v>
@@ -16070,7 +16070,7 @@
     </row>
     <row r="270" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A270" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B270" s="20">
         <v>14</v>
@@ -16088,10 +16088,10 @@
         <v>12.25</v>
       </c>
       <c r="G270" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H270" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I270" s="18">
         <v>12.284000000000001</v>
@@ -16127,7 +16127,7 @@
     </row>
     <row r="271" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A271" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B271" s="20">
         <v>14.15</v>
@@ -16145,10 +16145,10 @@
         <v>12.25</v>
       </c>
       <c r="G271" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H271" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I271" s="18">
         <v>12.286</v>
@@ -16180,7 +16180,7 @@
     </row>
     <row r="272" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A272" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B272" s="20">
         <v>16</v>
@@ -16198,10 +16198,10 @@
         <v>14.75</v>
       </c>
       <c r="G272" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H272" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I272" s="18">
         <v>14.813000000000001</v>
@@ -16239,7 +16239,7 @@
     </row>
     <row r="273" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A273" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B273" s="20">
         <v>16</v>
@@ -16258,7 +16258,7 @@
       </c>
       <c r="G273" s="17"/>
       <c r="H273" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I273" s="18">
         <v>14.635999999999999</v>
@@ -16296,7 +16296,7 @@
     </row>
     <row r="274" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A274" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B274" s="20">
         <v>16</v>
@@ -16314,10 +16314,10 @@
         <v>14.6</v>
       </c>
       <c r="G274" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H274" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I274" s="18">
         <v>14.673</v>
@@ -16355,7 +16355,7 @@
     </row>
     <row r="275" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A275" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B275" s="20">
         <v>16.079999999999998</v>
@@ -16373,10 +16373,10 @@
         <v>14.6</v>
       </c>
       <c r="G275" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H275" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I275" s="18">
         <v>14.673</v>
@@ -16408,7 +16408,7 @@
     </row>
     <row r="276" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A276" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B276" s="20">
         <v>16.149999999999999</v>
@@ -16426,10 +16426,10 @@
         <v>14.6</v>
       </c>
       <c r="G276" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H276" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I276" s="18">
         <v>14.673</v>
@@ -16461,7 +16461,7 @@
     </row>
     <row r="277" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A277" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B277" s="20">
         <v>16.149999999999999</v>
@@ -16479,10 +16479,10 @@
         <v>14.5</v>
       </c>
       <c r="G277" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H277" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I277" s="18">
         <v>14.573</v>
@@ -16514,7 +16514,7 @@
     </row>
     <row r="278" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A278" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B278" s="20">
         <v>16.2</v>
@@ -16532,10 +16532,10 @@
         <v>14.5</v>
       </c>
       <c r="G278" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H278" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I278" s="18">
         <v>14.573</v>
@@ -16567,7 +16567,7 @@
     </row>
     <row r="279" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A279" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B279" s="20">
         <v>16.25</v>
@@ -16585,10 +16585,10 @@
         <v>14.5</v>
       </c>
       <c r="G279" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H279" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I279" s="18">
         <v>14.573</v>
@@ -16648,6 +16648,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010086C7BD3502B74143933E9FF8B303809D" ma:contentTypeVersion="14" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="ca4566403a48b772521af487c6dcc89b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="e6f3eafb-35cb-45d6-a8b8-2cf7305da5b0" xmlns:ns4="127f82bc-20a5-4893-838d-120db4595288" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f4f9459af10a1f54b56fa50d6d80bae1" ns3:_="" ns4:_="">
     <xsd:import namespace="e6f3eafb-35cb-45d6-a8b8-2cf7305da5b0"/>
@@ -16874,15 +16883,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B9E616D-49B2-463C-8CB2-171BA13F16D3}">
   <ds:schemaRefs>
@@ -16901,6 +16901,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E657AC8E-10FC-40B3-949E-7B6780A595BF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1D1925A-4B91-4339-B88B-4DA6E99CBFBF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -16917,12 +16925,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E657AC8E-10FC-40B3-949E-7B6780A595BF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>